--- a/samples/edx/docs/samples/invoice.xlsx
+++ b/samples/edx/docs/samples/invoice.xlsx
@@ -28,40 +28,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>supplierName</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>supplierTaxId</t>
+          <t>customerTaxId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>customerTaxOffice</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>customerTaxId</t>
+          <t>customerDistrict</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>customerCity</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>customerCountry</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>unitCode</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>unitPrice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>vatRate</t>
         </is>
@@ -70,7 +85,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INV-2026-0001</t>
+          <t>ABC2026000000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -85,40 +100,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Veriban Yazilim A.S.</t>
+          <t>Bilgera Bilisim A.S.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>1234567802</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ornek Musteri Ltd.</t>
+          <t>Cankaya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0987654321</t>
+          <t>Cankaya</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Danismanlik hizmeti</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -162,20 +192,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Yazilim lisansi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>420.50</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
